--- a/pvz.xlsx
+++ b/pvz.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\taziz\Desktop\PVZ_BOT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{198F8C13-95F5-468D-A046-268E2F5FC317}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25D48C7D-7E26-49AA-A2AF-2950AE925F6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11325" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3878" uniqueCount="3875">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4010" uniqueCount="4004">
   <si>
     <t>Toshkent sh., Chilonzor tumani, 7-mavze, 45b-uy (Qatortol): г. Ташкент, Чиланзарский район, квартал-7, д 45б (Катартал)</t>
   </si>
@@ -11676,6 +11676,393 @@
   </si>
   <si>
     <t>72.321296</t>
+  </si>
+  <si>
+    <t>Saray sh., To‘raqo‘rg‘on tumani, Shovon ko'chasi, 2a uy: г. Сарай, Туракурганский район, улица Шовон, дом 2 а</t>
+  </si>
+  <si>
+    <t>FrСРЙ-1</t>
+  </si>
+  <si>
+    <t>Xalkobod sh., Pop tumani, Neftchi ko'chasi, 155 uy: г. Халкабад, Папский район, улица Нефтчи, дом 155</t>
+  </si>
+  <si>
+    <t>FrХКД-1</t>
+  </si>
+  <si>
+    <t>Gul sh., Rohat ko‘chasi, 1 uy: г. Гуль, улица Рохат, дом 1</t>
+  </si>
+  <si>
+    <t>FrГЛУ-1</t>
+  </si>
+  <si>
+    <t>Navoiy sh., Jasorat ko'chasi, 71 d uy: г. Навои, улица Джасорат, дом 71 д</t>
+  </si>
+  <si>
+    <t>FrНАВ-26</t>
+  </si>
+  <si>
+    <t>Unqo'rg'on sh., T.Ochilov ko‘chasi, 30 uy: г. Ункурган, улица Т. Очилов, дом 30</t>
+  </si>
+  <si>
+    <t>FrУНК-3</t>
+  </si>
+  <si>
+    <t>Baxshtepa sh., Sho‘rchi tumani, Tinchlik ko‘chasi, 14А uy: г. Бахштепа, Шурчинский район, улица Тинчлик, дом 14А</t>
+  </si>
+  <si>
+    <t>FrБАХ-1</t>
+  </si>
+  <si>
+    <t>Xos sh., Bekobod tumani, O.Tojiboyev ko‘chasi, 58 uy: г. Хасс, Бекабадский район, улица О. Тожибоев, дом 58</t>
+  </si>
+  <si>
+    <t>FrХАС-1</t>
+  </si>
+  <si>
+    <t>Poytug' sh., Yuksalish ko'chasi, 150 uy: г. Пайтуг, улица Юксалиш, дом 150</t>
+  </si>
+  <si>
+    <t>FrПТГ-2</t>
+  </si>
+  <si>
+    <t>Xazarasp sh., Ma'rifat ko'chasi, 312 uy: г. Хазарасп, улица Маърифат, дом 312</t>
+  </si>
+  <si>
+    <t>FrХЗР-3</t>
+  </si>
+  <si>
+    <t>Ko‘hna Katagon sh., G‘alaba ko'chasi, 4 a uy: г. Кухна Катагон, улица Галаба, дом 4 а</t>
+  </si>
+  <si>
+    <t>FrККН-1</t>
+  </si>
+  <si>
+    <t>Toshkent sh., Yangihayot tumani, 8 qurilish hududi, 41 uy: г. Ташкент, Янгихаётский район, 8 строительный участок, дом 41</t>
+  </si>
+  <si>
+    <t>FrТАШ-407</t>
+  </si>
+  <si>
+    <t>Toshkent sh., Yangihayot tumani, Navruz ko'chasi, 34 uy: г. Ташкент, Янгихаётский район, улица Навруз, дом 34</t>
+  </si>
+  <si>
+    <t>FrТАШ-419</t>
+  </si>
+  <si>
+    <t>Iskandariy sh., Pastdarg'om tumani,Iskandari qishlog‘i ko‘chasi, 13 uy: г. Искандари, Пастдаргомский район, улица Кишлак Искандари, дом 13</t>
+  </si>
+  <si>
+    <t>FrИСК-1</t>
+  </si>
+  <si>
+    <t>Toshkent sh., Sirg'ali tumani, Sergeli Yo‘li shohko‘chasi,4 mavzesi, 17А uy: г. Ташкент, Сергелийский район, проспект Сергели Йули, 4 массив, дом 17А</t>
+  </si>
+  <si>
+    <t>FrТАШ-418</t>
+  </si>
+  <si>
+    <t>Namangan sh., 5 Do‘stlik yo‘lagi: г. Наманган, 5-й проезд Дустлик</t>
+  </si>
+  <si>
+    <t>FrНАМ-32</t>
+  </si>
+  <si>
+    <t>Andijon sh., Yo‘ldoshev ko‘chasi, 58 uy: г. Андижан, улица Юлдашева, дом 58</t>
+  </si>
+  <si>
+    <t>FrАНД-29</t>
+  </si>
+  <si>
+    <t>Uzun sh., Uzun tumani, O'zbekiston ko'chasi, 172 uy: г. Узун, Узунский район, улица Узбекистан, дом 172</t>
+  </si>
+  <si>
+    <t>FrУЗУ-4</t>
+  </si>
+  <si>
+    <t>Buxoro sh., M.Karim ko'chasi, 44 uy: г. Бухара, улица М. Каримова, дом 44</t>
+  </si>
+  <si>
+    <t>FrБХР-38</t>
+  </si>
+  <si>
+    <t>Uchquduq sh., Yoʻlchilar OFY, Gulshan ko'chasi, 61 B uy: г. Учкудук, МСГ Йулчилар, улица Гулшан, дом 61 б</t>
+  </si>
+  <si>
+    <t>FrУЧК-5</t>
+  </si>
+  <si>
+    <t>Toshkent sh., Olmazor tumani, Shifokorlar ko'chasi,Xo‘jayev mavzesi 5 a uy: г. Ташкент, Алмазарский район, улица Шифокорлар, массив Ходжаева, дом 5 а</t>
+  </si>
+  <si>
+    <t>FrТАШ-414</t>
+  </si>
+  <si>
+    <t>Toshkent sh., Olmazor tumani, Qora-qamish 1/3 mavzesi, 46 uy: г. Ташкент, Алмазарский район, массив Кара-Камыш квартал 1/3, дом 46</t>
+  </si>
+  <si>
+    <t>FrТАШ-415</t>
+  </si>
+  <si>
+    <t>Toshkent sh., Mirzo Ulug'bek tumani, Quva ko'chasi, 7/2 uy: г. Ташкент, Мирзо Улугбекский район, улица Кувинская, дом 7/2</t>
+  </si>
+  <si>
+    <t>FrТАШ-416</t>
+  </si>
+  <si>
+    <t>FrТАШ-410</t>
+  </si>
+  <si>
+    <t>Chelak sh., Chelaktepa ko'chasi, 26 uy: г. Челек, улица Челактепа, дом 26</t>
+  </si>
+  <si>
+    <t>FrЧЕЛ-3</t>
+  </si>
+  <si>
+    <t>Jiankekka sh., Termiziy ko'chasi, 92 uy: г. Джанчекка, улица Термизий, дом 92</t>
+  </si>
+  <si>
+    <t>FrДНЧ-1</t>
+  </si>
+  <si>
+    <t>Toshkent sh., Chilonzor tumani, Al-Xorazmiy 1 mavzesi, Zargarlik ko'chas, 12А uy: г. Ташкент, Чиланзарский район, массив Аль Хорезми 1, улица Заргарлик, дом 12А</t>
+  </si>
+  <si>
+    <t>FrТАШ-417</t>
+  </si>
+  <si>
+    <t>Tut sh., Jomboy tumani, Tut Kishlak ko'chasi, 222 uy: г. Тут, Джамбайский район, улица Кишлак Тут, дом 222</t>
+  </si>
+  <si>
+    <t>FrТУТ-1</t>
+  </si>
+  <si>
+    <t>Ko'ksaroy sh., Shifobaxsh suvlar, 115 uy: г. Куксарай, улица Шифобахш сувлар, дом 115</t>
+  </si>
+  <si>
+    <t>FrККС-2</t>
+  </si>
+  <si>
+    <t>Karmana sh., Obranon ko'chasi, 71 uy: г. Кармана, улица Обранон, дом 71</t>
+  </si>
+  <si>
+    <t>FrКРМ-6</t>
+  </si>
+  <si>
+    <t>Yangi Kuch sh., Uzun tumani, Tadbirkorlar ko‘chasi, 104 uy: г. Янгикуч, Узунский район, улица Тадбиркорлар, дом 104</t>
+  </si>
+  <si>
+    <t>FrЯГК-1</t>
+  </si>
+  <si>
+    <t>Gulbog sh., Navbahor tumani, Yangi yo'l ko'chasi, 276 uy: г. Гулбог, Навбахорский район, улица Янги Йул, дом 276</t>
+  </si>
+  <si>
+    <t>FrГБГ-1</t>
+  </si>
+  <si>
+    <t>Bog‘bon sh., Bulung'ur tumani, Yangiobod ko'chasi, 35 uy: г. Богбон, Булунгурский район, улица Янгиабад, дом 35</t>
+  </si>
+  <si>
+    <t>FrБГБ-1</t>
+  </si>
+  <si>
+    <t>Toshkent sh., Yangihayot tumani, Sergeli-6а massivi, 16 uy: г. Ташкент, Янгихаётский район, массив Сергели-6а, дом 16</t>
+  </si>
+  <si>
+    <t>FrТАШ-412</t>
+  </si>
+  <si>
+    <t>40.893128</t>
+  </si>
+  <si>
+    <t>71.510271</t>
+  </si>
+  <si>
+    <t>40.897697</t>
+  </si>
+  <si>
+    <t>71.147597</t>
+  </si>
+  <si>
+    <t>40.851696</t>
+  </si>
+  <si>
+    <t>68.798134</t>
+  </si>
+  <si>
+    <t>40.114909</t>
+  </si>
+  <si>
+    <t>65.370251</t>
+  </si>
+  <si>
+    <t>41.399101</t>
+  </si>
+  <si>
+    <t>69.337647</t>
+  </si>
+  <si>
+    <t>38.065112</t>
+  </si>
+  <si>
+    <t>67.761333</t>
+  </si>
+  <si>
+    <t>40.274513</t>
+  </si>
+  <si>
+    <t>69.201252</t>
+  </si>
+  <si>
+    <t>40.905269</t>
+  </si>
+  <si>
+    <t>72.247982</t>
+  </si>
+  <si>
+    <t>41.284100</t>
+  </si>
+  <si>
+    <t>61.216800</t>
+  </si>
+  <si>
+    <t>39.040728</t>
+  </si>
+  <si>
+    <t>65.454414</t>
+  </si>
+  <si>
+    <t>41.212417</t>
+  </si>
+  <si>
+    <t>69.193400</t>
+  </si>
+  <si>
+    <t>41.222339</t>
+  </si>
+  <si>
+    <t>69.192400</t>
+  </si>
+  <si>
+    <t>39.693623</t>
+  </si>
+  <si>
+    <t>66.758091</t>
+  </si>
+  <si>
+    <t>41.215458</t>
+  </si>
+  <si>
+    <t>69.243947</t>
+  </si>
+  <si>
+    <t>41.011804</t>
+  </si>
+  <si>
+    <t>71.616891</t>
+  </si>
+  <si>
+    <t>40.748197</t>
+  </si>
+  <si>
+    <t>72.322634</t>
+  </si>
+  <si>
+    <t>38.373020</t>
+  </si>
+  <si>
+    <t>68.014789</t>
+  </si>
+  <si>
+    <t>39.782283</t>
+  </si>
+  <si>
+    <t>64.400923</t>
+  </si>
+  <si>
+    <t>42.170835</t>
+  </si>
+  <si>
+    <t>63.583985</t>
+  </si>
+  <si>
+    <t>41.357197</t>
+  </si>
+  <si>
+    <t>69.183859</t>
+  </si>
+  <si>
+    <t>41.358750</t>
+  </si>
+  <si>
+    <t>69.229394</t>
+  </si>
+  <si>
+    <t>41.316583</t>
+  </si>
+  <si>
+    <t>69.356947</t>
+  </si>
+  <si>
+    <t>39.930082</t>
+  </si>
+  <si>
+    <t>66.858512</t>
+  </si>
+  <si>
+    <t>38.353594</t>
+  </si>
+  <si>
+    <t>68.075375</t>
+  </si>
+  <si>
+    <t>41.257445</t>
+  </si>
+  <si>
+    <t>69.158576</t>
+  </si>
+  <si>
+    <t>39.765655</t>
+  </si>
+  <si>
+    <t>66.988887</t>
+  </si>
+  <si>
+    <t>41.353822</t>
+  </si>
+  <si>
+    <t>69.141917</t>
+  </si>
+  <si>
+    <t>40.142709</t>
+  </si>
+  <si>
+    <t>65.386332</t>
+  </si>
+  <si>
+    <t>38.370279</t>
+  </si>
+  <si>
+    <t>68.022203</t>
+  </si>
+  <si>
+    <t>40.186192</t>
+  </si>
+  <si>
+    <t>65.357881</t>
+  </si>
+  <si>
+    <t>39.786100</t>
+  </si>
+  <si>
+    <t>67.249700</t>
+  </si>
+  <si>
+    <t>41.214000</t>
+  </si>
+  <si>
+    <t>69.208600</t>
   </si>
 </sst>
 </file>
@@ -11958,7 +12345,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -12099,6 +12486,9 @@
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -12381,7 +12771,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D1594"/>
+  <dimension ref="A1:D1627"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="39.5703125" customWidth="1"/>
@@ -34707,6 +35097,468 @@
         <v>3874</v>
       </c>
     </row>
+    <row r="1595" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1595" s="7" t="s">
+        <v>3875</v>
+      </c>
+      <c r="B1595" s="41" t="s">
+        <v>3876</v>
+      </c>
+      <c r="C1595" s="43" t="s">
+        <v>3940</v>
+      </c>
+      <c r="D1595" s="10" t="s">
+        <v>3941</v>
+      </c>
+    </row>
+    <row r="1596" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1596" s="5" t="s">
+        <v>3877</v>
+      </c>
+      <c r="B1596" s="42" t="s">
+        <v>3878</v>
+      </c>
+      <c r="C1596" s="44" t="s">
+        <v>3942</v>
+      </c>
+      <c r="D1596" s="10" t="s">
+        <v>3943</v>
+      </c>
+    </row>
+    <row r="1597" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1597" s="5" t="s">
+        <v>3879</v>
+      </c>
+      <c r="B1597" s="42" t="s">
+        <v>3880</v>
+      </c>
+      <c r="C1597" s="44" t="s">
+        <v>3944</v>
+      </c>
+      <c r="D1597" s="10" t="s">
+        <v>3945</v>
+      </c>
+    </row>
+    <row r="1598" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1598" s="5" t="s">
+        <v>3881</v>
+      </c>
+      <c r="B1598" s="42" t="s">
+        <v>3882</v>
+      </c>
+      <c r="C1598" s="44" t="s">
+        <v>3946</v>
+      </c>
+      <c r="D1598" s="10" t="s">
+        <v>3947</v>
+      </c>
+    </row>
+    <row r="1599" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1599" s="5" t="s">
+        <v>3883</v>
+      </c>
+      <c r="B1599" s="42" t="s">
+        <v>3884</v>
+      </c>
+      <c r="C1599" s="44" t="s">
+        <v>3948</v>
+      </c>
+      <c r="D1599" s="10" t="s">
+        <v>3949</v>
+      </c>
+    </row>
+    <row r="1600" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1600" s="5" t="s">
+        <v>3885</v>
+      </c>
+      <c r="B1600" s="42" t="s">
+        <v>3886</v>
+      </c>
+      <c r="C1600" s="44" t="s">
+        <v>3950</v>
+      </c>
+      <c r="D1600" s="10" t="s">
+        <v>3951</v>
+      </c>
+    </row>
+    <row r="1601" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1601" s="5" t="s">
+        <v>3887</v>
+      </c>
+      <c r="B1601" s="42" t="s">
+        <v>3888</v>
+      </c>
+      <c r="C1601" s="44" t="s">
+        <v>3952</v>
+      </c>
+      <c r="D1601" s="10" t="s">
+        <v>3953</v>
+      </c>
+    </row>
+    <row r="1602" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1602" s="5" t="s">
+        <v>3889</v>
+      </c>
+      <c r="B1602" s="42" t="s">
+        <v>3890</v>
+      </c>
+      <c r="C1602" s="44" t="s">
+        <v>3954</v>
+      </c>
+      <c r="D1602" s="10" t="s">
+        <v>3955</v>
+      </c>
+    </row>
+    <row r="1603" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1603" s="5" t="s">
+        <v>3891</v>
+      </c>
+      <c r="B1603" s="42" t="s">
+        <v>3892</v>
+      </c>
+      <c r="C1603" s="44" t="s">
+        <v>3956</v>
+      </c>
+      <c r="D1603" s="10" t="s">
+        <v>3957</v>
+      </c>
+    </row>
+    <row r="1604" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1604" s="5" t="s">
+        <v>3893</v>
+      </c>
+      <c r="B1604" s="42" t="s">
+        <v>3894</v>
+      </c>
+      <c r="C1604" s="44" t="s">
+        <v>3958</v>
+      </c>
+      <c r="D1604" s="10" t="s">
+        <v>3959</v>
+      </c>
+    </row>
+    <row r="1605" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1605" s="2" t="s">
+        <v>3895</v>
+      </c>
+      <c r="B1605" s="42" t="s">
+        <v>3896</v>
+      </c>
+      <c r="C1605" s="47" t="s">
+        <v>3960</v>
+      </c>
+      <c r="D1605" s="10" t="s">
+        <v>3961</v>
+      </c>
+    </row>
+    <row r="1606" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1606" s="5" t="s">
+        <v>3897</v>
+      </c>
+      <c r="B1606" s="42" t="s">
+        <v>3898</v>
+      </c>
+      <c r="C1606" s="44" t="s">
+        <v>3962</v>
+      </c>
+      <c r="D1606" s="10" t="s">
+        <v>3963</v>
+      </c>
+    </row>
+    <row r="1607" spans="1:4" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1607" s="5" t="s">
+        <v>3899</v>
+      </c>
+      <c r="B1607" s="48" t="s">
+        <v>3900</v>
+      </c>
+      <c r="C1607" s="44" t="s">
+        <v>3964</v>
+      </c>
+      <c r="D1607" s="10" t="s">
+        <v>3965</v>
+      </c>
+    </row>
+    <row r="1608" spans="1:4" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1608" s="5" t="s">
+        <v>3901</v>
+      </c>
+      <c r="B1608" s="42" t="s">
+        <v>3902</v>
+      </c>
+      <c r="C1608" s="44" t="s">
+        <v>3966</v>
+      </c>
+      <c r="D1608" s="10" t="s">
+        <v>3967</v>
+      </c>
+    </row>
+    <row r="1609" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1609" s="5" t="s">
+        <v>3903</v>
+      </c>
+      <c r="B1609" s="42" t="s">
+        <v>3904</v>
+      </c>
+      <c r="C1609" s="44" t="s">
+        <v>3968</v>
+      </c>
+      <c r="D1609" s="10" t="s">
+        <v>3969</v>
+      </c>
+    </row>
+    <row r="1610" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1610" s="5" t="s">
+        <v>3905</v>
+      </c>
+      <c r="B1610" s="42" t="s">
+        <v>3906</v>
+      </c>
+      <c r="C1610" s="44" t="s">
+        <v>3970</v>
+      </c>
+      <c r="D1610" s="10" t="s">
+        <v>3971</v>
+      </c>
+    </row>
+    <row r="1611" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1611" s="5" t="s">
+        <v>3907</v>
+      </c>
+      <c r="B1611" s="42" t="s">
+        <v>3908</v>
+      </c>
+      <c r="C1611" s="44" t="s">
+        <v>3972</v>
+      </c>
+      <c r="D1611" s="10" t="s">
+        <v>3973</v>
+      </c>
+    </row>
+    <row r="1612" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1612" s="5" t="s">
+        <v>3909</v>
+      </c>
+      <c r="B1612" s="42" t="s">
+        <v>3910</v>
+      </c>
+      <c r="C1612" s="44" t="s">
+        <v>3974</v>
+      </c>
+      <c r="D1612" s="10" t="s">
+        <v>3975</v>
+      </c>
+    </row>
+    <row r="1613" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1613" s="5" t="s">
+        <v>3911</v>
+      </c>
+      <c r="B1613" s="42" t="s">
+        <v>3912</v>
+      </c>
+      <c r="C1613" s="44" t="s">
+        <v>3976</v>
+      </c>
+      <c r="D1613" s="10" t="s">
+        <v>3977</v>
+      </c>
+    </row>
+    <row r="1614" spans="1:4" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1614" s="5" t="s">
+        <v>3913</v>
+      </c>
+      <c r="B1614" s="42" t="s">
+        <v>3914</v>
+      </c>
+      <c r="C1614" s="44" t="s">
+        <v>3978</v>
+      </c>
+      <c r="D1614" s="10" t="s">
+        <v>3979</v>
+      </c>
+    </row>
+    <row r="1615" spans="1:4" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1615" s="5" t="s">
+        <v>3915</v>
+      </c>
+      <c r="B1615" s="42" t="s">
+        <v>3916</v>
+      </c>
+      <c r="C1615" s="44" t="s">
+        <v>3980</v>
+      </c>
+      <c r="D1615" s="10" t="s">
+        <v>3981</v>
+      </c>
+    </row>
+    <row r="1616" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1616" s="5" t="s">
+        <v>3917</v>
+      </c>
+      <c r="B1616" s="42" t="s">
+        <v>3918</v>
+      </c>
+      <c r="C1616" s="44" t="s">
+        <v>3982</v>
+      </c>
+      <c r="D1616" s="10" t="s">
+        <v>3983</v>
+      </c>
+    </row>
+    <row r="1617" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1617" s="5" t="s">
+        <v>3814</v>
+      </c>
+      <c r="B1617" s="42" t="s">
+        <v>3919</v>
+      </c>
+      <c r="C1617" s="44" t="s">
+        <v>3845</v>
+      </c>
+      <c r="D1617" s="10" t="s">
+        <v>3846</v>
+      </c>
+    </row>
+    <row r="1618" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1618" s="5" t="s">
+        <v>3920</v>
+      </c>
+      <c r="B1618" s="42" t="s">
+        <v>3921</v>
+      </c>
+      <c r="C1618" s="44" t="s">
+        <v>3984</v>
+      </c>
+      <c r="D1618" s="10" t="s">
+        <v>3985</v>
+      </c>
+    </row>
+    <row r="1619" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1619" s="5" t="s">
+        <v>3922</v>
+      </c>
+      <c r="B1619" s="42" t="s">
+        <v>3923</v>
+      </c>
+      <c r="C1619" s="44" t="s">
+        <v>3986</v>
+      </c>
+      <c r="D1619" s="10" t="s">
+        <v>3987</v>
+      </c>
+    </row>
+    <row r="1620" spans="1:4" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1620" s="5" t="s">
+        <v>3924</v>
+      </c>
+      <c r="B1620" s="42" t="s">
+        <v>3925</v>
+      </c>
+      <c r="C1620" s="44" t="s">
+        <v>3988</v>
+      </c>
+      <c r="D1620" s="10" t="s">
+        <v>3989</v>
+      </c>
+    </row>
+    <row r="1621" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1621" s="5" t="s">
+        <v>3926</v>
+      </c>
+      <c r="B1621" s="42" t="s">
+        <v>3927</v>
+      </c>
+      <c r="C1621" s="44" t="s">
+        <v>3990</v>
+      </c>
+      <c r="D1621" s="10" t="s">
+        <v>3991</v>
+      </c>
+    </row>
+    <row r="1622" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1622" s="5" t="s">
+        <v>3928</v>
+      </c>
+      <c r="B1622" s="42" t="s">
+        <v>3929</v>
+      </c>
+      <c r="C1622" s="44" t="s">
+        <v>3992</v>
+      </c>
+      <c r="D1622" s="10" t="s">
+        <v>3993</v>
+      </c>
+    </row>
+    <row r="1623" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1623" s="5" t="s">
+        <v>3930</v>
+      </c>
+      <c r="B1623" s="42" t="s">
+        <v>3931</v>
+      </c>
+      <c r="C1623" s="44" t="s">
+        <v>3994</v>
+      </c>
+      <c r="D1623" s="10" t="s">
+        <v>3995</v>
+      </c>
+    </row>
+    <row r="1624" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1624" s="5" t="s">
+        <v>3932</v>
+      </c>
+      <c r="B1624" s="42" t="s">
+        <v>3933</v>
+      </c>
+      <c r="C1624" s="44" t="s">
+        <v>3996</v>
+      </c>
+      <c r="D1624" s="10" t="s">
+        <v>3997</v>
+      </c>
+    </row>
+    <row r="1625" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1625" s="5" t="s">
+        <v>3934</v>
+      </c>
+      <c r="B1625" s="42" t="s">
+        <v>3935</v>
+      </c>
+      <c r="C1625" s="44" t="s">
+        <v>3998</v>
+      </c>
+      <c r="D1625" s="10" t="s">
+        <v>3999</v>
+      </c>
+    </row>
+    <row r="1626" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1626" s="5" t="s">
+        <v>3936</v>
+      </c>
+      <c r="B1626" s="42" t="s">
+        <v>3937</v>
+      </c>
+      <c r="C1626" s="44" t="s">
+        <v>4000</v>
+      </c>
+      <c r="D1626" s="10" t="s">
+        <v>4001</v>
+      </c>
+    </row>
+    <row r="1627" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1627" s="5" t="s">
+        <v>3938</v>
+      </c>
+      <c r="B1627" s="42" t="s">
+        <v>3939</v>
+      </c>
+      <c r="C1627" s="44" t="s">
+        <v>4002</v>
+      </c>
+      <c r="D1627" s="10" t="s">
+        <v>4003</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/pvz.xlsx
+++ b/pvz.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\taziz\Desktop\PVZ_BOT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25D48C7D-7E26-49AA-A2AF-2950AE925F6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFB8CE91-0A58-4B29-A789-217F546B92BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1950" yWindow="1950" windowWidth="21600" windowHeight="11325" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4010" uniqueCount="4004">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4034" uniqueCount="4028">
   <si>
     <t>Toshkent sh., Chilonzor tumani, 7-mavze, 45b-uy (Qatortol): г. Ташкент, Чиланзарский район, квартал-7, д 45б (Катартал)</t>
   </si>
@@ -12063,6 +12063,78 @@
   </si>
   <si>
     <t>69.208600</t>
+  </si>
+  <si>
+    <t>Chinoz sh., Gulzorobod ko'chasi, 10 uy: г. Чиназ, улица Гулзоробод, дом 10</t>
+  </si>
+  <si>
+    <t>FrЧИН-8</t>
+  </si>
+  <si>
+    <t>Andijon sh., Cho'lpon shoh ko'chasi, 185 uy: г. Андижан, проспект Чулпон, 185 дом</t>
+  </si>
+  <si>
+    <t>FrАНД-30</t>
+  </si>
+  <si>
+    <t>Olmaliq sh., Furqat ko'chasi, 4 uy: г. Алмалык, улица Фурката, дом 4</t>
+  </si>
+  <si>
+    <t>FrАЛМ-18</t>
+  </si>
+  <si>
+    <t>Karvak sh., Xazorasp tumani, Yoshlar ko‘chasi, 21 uy: г. Карвак, улица Ёшлар, дом 21</t>
+  </si>
+  <si>
+    <t>FrКРВ-1</t>
+  </si>
+  <si>
+    <t>Yangi Nishon sh., Yangi xayot ko'chasi, 65 uy: г. Янги Нишан, улица Янгихаёт, дом 65</t>
+  </si>
+  <si>
+    <t>FrЯНШ-3</t>
+  </si>
+  <si>
+    <t>Jizzax sh., Zargarlik ko‘chasi, 89 uy: г. Джизак , улица Заргарлик , 89 дом</t>
+  </si>
+  <si>
+    <t>FrДЗК-18</t>
+  </si>
+  <si>
+    <t>40.922263</t>
+  </si>
+  <si>
+    <t>68.760517</t>
+  </si>
+  <si>
+    <t>40.793287</t>
+  </si>
+  <si>
+    <t>72.347952</t>
+  </si>
+  <si>
+    <t>40.852822</t>
+  </si>
+  <si>
+    <t>69.599956</t>
+  </si>
+  <si>
+    <t>41.288386</t>
+  </si>
+  <si>
+    <t>61.188530</t>
+  </si>
+  <si>
+    <t>38.617091</t>
+  </si>
+  <si>
+    <t>65.681129</t>
+  </si>
+  <si>
+    <t>40.097550</t>
+  </si>
+  <si>
+    <t>67.836259</t>
   </si>
 </sst>
 </file>
@@ -12771,7 +12843,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D1627"/>
+  <dimension ref="A1:D1633"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="39.5703125" customWidth="1"/>
@@ -35559,6 +35631,90 @@
         <v>4003</v>
       </c>
     </row>
+    <row r="1628" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1628" s="7" t="s">
+        <v>4004</v>
+      </c>
+      <c r="B1628" s="41" t="s">
+        <v>4005</v>
+      </c>
+      <c r="C1628" s="43" t="s">
+        <v>4016</v>
+      </c>
+      <c r="D1628" s="10" t="s">
+        <v>4017</v>
+      </c>
+    </row>
+    <row r="1629" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1629" s="5" t="s">
+        <v>4006</v>
+      </c>
+      <c r="B1629" s="42" t="s">
+        <v>4007</v>
+      </c>
+      <c r="C1629" s="44" t="s">
+        <v>4018</v>
+      </c>
+      <c r="D1629" s="10" t="s">
+        <v>4019</v>
+      </c>
+    </row>
+    <row r="1630" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1630" s="5" t="s">
+        <v>4008</v>
+      </c>
+      <c r="B1630" s="42" t="s">
+        <v>4009</v>
+      </c>
+      <c r="C1630" s="44" t="s">
+        <v>4020</v>
+      </c>
+      <c r="D1630" s="10" t="s">
+        <v>4021</v>
+      </c>
+    </row>
+    <row r="1631" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1631" s="5" t="s">
+        <v>4010</v>
+      </c>
+      <c r="B1631" s="42" t="s">
+        <v>4011</v>
+      </c>
+      <c r="C1631" s="44" t="s">
+        <v>4022</v>
+      </c>
+      <c r="D1631" s="10" t="s">
+        <v>4023</v>
+      </c>
+    </row>
+    <row r="1632" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1632" s="5" t="s">
+        <v>4012</v>
+      </c>
+      <c r="B1632" s="42" t="s">
+        <v>4013</v>
+      </c>
+      <c r="C1632" s="44" t="s">
+        <v>4024</v>
+      </c>
+      <c r="D1632" s="10" t="s">
+        <v>4025</v>
+      </c>
+    </row>
+    <row r="1633" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1633" s="5" t="s">
+        <v>4014</v>
+      </c>
+      <c r="B1633" s="42" t="s">
+        <v>4015</v>
+      </c>
+      <c r="C1633" s="44" t="s">
+        <v>4026</v>
+      </c>
+      <c r="D1633" s="10" t="s">
+        <v>4027</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/pvz.xlsx
+++ b/pvz.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\taziz\Desktop\PVZ_BOT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFB8CE91-0A58-4B29-A789-217F546B92BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEFDB326-63FD-49E3-B502-FFA3AD735D70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1950" yWindow="1950" windowWidth="21600" windowHeight="11325" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4034" uniqueCount="4028">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4042" uniqueCount="4036">
   <si>
     <t>Toshkent sh., Chilonzor tumani, 7-mavze, 45b-uy (Qatortol): г. Ташкент, Чиланзарский район, квартал-7, д 45б (Катартал)</t>
   </si>
@@ -12135,6 +12135,30 @@
   </si>
   <si>
     <t>67.836259</t>
+  </si>
+  <si>
+    <t>FrХАВ-4</t>
+  </si>
+  <si>
+    <t>FrКМШ-4</t>
+  </si>
+  <si>
+    <t>Xovos sh., Gulbahor MFY, Hamza ko'chasi, 1 uy: г. Хаваст, Гулбахор МФИ, улица Хамза, дом 1         +998941873506</t>
+  </si>
+  <si>
+    <t>Qamashi sh., Yuksalish MFY, Olchabog' ko'chasi, 313 uy: г. Камаши, Юксалиш МФИ, улица Олчабог, дом 313     +998509076907</t>
+  </si>
+  <si>
+    <t>40.244295</t>
+  </si>
+  <si>
+    <t>68.890891</t>
+  </si>
+  <si>
+    <t>38.799952</t>
+  </si>
+  <si>
+    <t>66.536379</t>
   </si>
 </sst>
 </file>
@@ -12843,7 +12867,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D1633"/>
+  <dimension ref="A1:D1635"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="39.5703125" customWidth="1"/>
@@ -35715,6 +35739,34 @@
         <v>4027</v>
       </c>
     </row>
+    <row r="1634" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1634" s="7" t="s">
+        <v>4030</v>
+      </c>
+      <c r="B1634" s="41" t="s">
+        <v>4028</v>
+      </c>
+      <c r="C1634" s="43" t="s">
+        <v>4032</v>
+      </c>
+      <c r="D1634" s="10" t="s">
+        <v>4033</v>
+      </c>
+    </row>
+    <row r="1635" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1635" s="5" t="s">
+        <v>4031</v>
+      </c>
+      <c r="B1635" s="42" t="s">
+        <v>4029</v>
+      </c>
+      <c r="C1635" s="44" t="s">
+        <v>4034</v>
+      </c>
+      <c r="D1635" s="10" t="s">
+        <v>4035</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/pvz.xlsx
+++ b/pvz.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\taziz\Desktop\PVZ_BOT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57E6C13F-7D10-403C-B436-4F681656F40E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70936B39-E442-43D7-8F39-BDEEBDD381E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1515" yWindow="1515" windowWidth="21600" windowHeight="11325" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6543" uniqueCount="6539">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6653" uniqueCount="6649">
   <si>
     <t>Toshkent sh., Chilonzor tumani, 7-mavze, 45b-uy (Qatortol): г. Ташкент, Чиланзарский район, квартал-7, д 45б (Катартал)</t>
   </si>
@@ -19653,18 +19653,356 @@
   </si>
   <si>
     <t>40.435365, 70.593504</t>
+  </si>
+  <si>
+    <t>Xaqqulobod sh., Norin tumani, Beruniy ko'chasi, 20 uy: г. Хаккулабад, Норинский район, улица Беруни, дом 20</t>
+  </si>
+  <si>
+    <t>FrХАК-4</t>
+  </si>
+  <si>
+    <t>998 70 015 92 04</t>
+  </si>
+  <si>
+    <t>@UzumFrXAK4</t>
+  </si>
+  <si>
+    <t>40.910345, 72.120678</t>
+  </si>
+  <si>
+    <t>Zohidon sh., Rishton tumani, Muqimiy ko‘chasi, 12 uy: г. Захидан, Риштанский район, улица Мукимий, дом 12</t>
+  </si>
+  <si>
+    <t>FrЗХИ-1</t>
+  </si>
+  <si>
+    <t>998 50 508 97 50</t>
+  </si>
+  <si>
+    <t>@UzumFrZXI1</t>
+  </si>
+  <si>
+    <t>40.395435, 71.282701</t>
+  </si>
+  <si>
+    <t>Gulbaxor sh., Yangiyo'l tumani, Turon ko'chasi, 184 uy: г. Гульбахор, Янгиюльский район, улица Туран, дом 184</t>
+  </si>
+  <si>
+    <t>FrГБХ-3</t>
+  </si>
+  <si>
+    <t>998 99 002 85 96</t>
+  </si>
+  <si>
+    <t>@FrGBX3</t>
+  </si>
+  <si>
+    <t>41.079084, 69.029166</t>
+  </si>
+  <si>
+    <t>Toshkent sh., Olmazor tumani, Qorasqamish 3 ko'chasi, 3А uy: г. Ташкент, Алмазарский район, улица 3 Каракамыш, дом 3А</t>
+  </si>
+  <si>
+    <t>FrТАШ-429</t>
+  </si>
+  <si>
+    <t>998 88 000 74 79</t>
+  </si>
+  <si>
+    <t>@FrTASH_429</t>
+  </si>
+  <si>
+    <t>41.370822, 69.209479</t>
+  </si>
+  <si>
+    <t>Charxin sh., Tinchlik MFY, Samarqand ko'chasi, 18 uy: г. Чархин, Тинчлик МСГ, улица Самарканд, дом 18</t>
+  </si>
+  <si>
+    <t>FrЧРХ-3</t>
+  </si>
+  <si>
+    <t>998 90 609 02 98</t>
+  </si>
+  <si>
+    <t>@fr_chrx_3</t>
+  </si>
+  <si>
+    <t>39.700127, 66.821433</t>
+  </si>
+  <si>
+    <t>Xonziq sh., Farg‘ona tumani, Bunyodkor ko'chasi, 105 uy: г. Ханкиз, Ферганский район, улица Бунёдкор, дом 105</t>
+  </si>
+  <si>
+    <t>FrХНЗ-1</t>
+  </si>
+  <si>
+    <t>998 95 370 00 19</t>
+  </si>
+  <si>
+    <t>@uzumxnz1</t>
+  </si>
+  <si>
+    <t>40.286830, 71.506739</t>
+  </si>
+  <si>
+    <t>Samarqand sh., Koziarik MFY, Mehroj ko'chasi, 45 uy: г. Самарканд, Козиарик МСГ, улица Мехрож, дом 45</t>
+  </si>
+  <si>
+    <t>FrСМК-80</t>
+  </si>
+  <si>
+    <t>998 70 167 56 78</t>
+  </si>
+  <si>
+    <t>@fr_smk_80</t>
+  </si>
+  <si>
+    <t>39.663906, 67.010538</t>
+  </si>
+  <si>
+    <t>Beshbola sh., Pastdarg'om tumani, Qishloq ochchi ko'chasi, 284 uy: г. Бешбола, Пастдаргомский район, улица Кишлак Аччи, дом 284</t>
+  </si>
+  <si>
+    <t>FrБЛА-1</t>
+  </si>
+  <si>
+    <t>998 77 971 71 07</t>
+  </si>
+  <si>
+    <t>@fr_bla_1</t>
+  </si>
+  <si>
+    <t>39.735946, 66.700182</t>
+  </si>
+  <si>
+    <t>Jarqoʻrgʻon sh., Markaziy Surxon MFY, Maorifchilar 1 ko'chasi, 6 v uy: г. Джаркурган, Марказий Сурхон МФИ, улица Маорифчилар 1 , дом 6 в</t>
+  </si>
+  <si>
+    <t>FrДЖР-4</t>
+  </si>
+  <si>
+    <t>998 77 161 04 97</t>
+  </si>
+  <si>
+    <t>@FrDjr4</t>
+  </si>
+  <si>
+    <t>37.736974, 67.508742</t>
+  </si>
+  <si>
+    <t>Vaxim sh., Shaxrixon tumani, Vaxim 1 ko'chasi, 278 uy: г. Вахим, Шахриханский район, улица Вахим 1, дом 278</t>
+  </si>
+  <si>
+    <t>FrВХМ-1</t>
+  </si>
+  <si>
+    <t>998 95 725 24 98</t>
+  </si>
+  <si>
+    <t>@FrBXM_1</t>
+  </si>
+  <si>
+    <t>40.743283, 72.043400</t>
+  </si>
+  <si>
+    <t>Toshkent sh., Chilonzor tumani, Olmazor dahasi, 15/3: г. Ташкент, Чиланзарский район, микрорайон Алмазар, дом 15/3</t>
+  </si>
+  <si>
+    <t>FrТАШ-428</t>
+  </si>
+  <si>
+    <t>998 50 733 62 95</t>
+  </si>
+  <si>
+    <t>@FrTash_428</t>
+  </si>
+  <si>
+    <t>41.306731, 69.245998</t>
+  </si>
+  <si>
+    <t>Jizzax sh., Sayiljoyi ko‘chasi, 61 uy: г. Джизак, улица Сайилжойи, дом 61</t>
+  </si>
+  <si>
+    <t>FrДЗК-21</t>
+  </si>
+  <si>
+    <t>998 95 394 90 40</t>
+  </si>
+  <si>
+    <t>@FrDZK21</t>
+  </si>
+  <si>
+    <t>40.130898, 67.820805</t>
+  </si>
+  <si>
+    <t>Bo'ston sh., Oybek ko'chasi, 386 uy: г. Бустан, улица Айбека, дом 386</t>
+  </si>
+  <si>
+    <t>FrБТН-3</t>
+  </si>
+  <si>
+    <t>998 93 604 96 00</t>
+  </si>
+  <si>
+    <t>@FrBTH_3</t>
+  </si>
+  <si>
+    <t>41.853821, 60.929602</t>
+  </si>
+  <si>
+    <t>Andijon sh., Alisher Navoiy shoh ko'chasi, 8 uy: г. Андижан, проспект Алишера Навои, 8 дом</t>
+  </si>
+  <si>
+    <t>FrАНД-33</t>
+  </si>
+  <si>
+    <t>998 88 981 12 22</t>
+  </si>
+  <si>
+    <t>@UzumFrAND33_1981</t>
+  </si>
+  <si>
+    <t>40.765214, 72.364813</t>
+  </si>
+  <si>
+    <t>Chinoz sh., Oxunboboyev ko'chasi, 57 uy: г. Чиназ, улица Ахунбабаева, дом 57</t>
+  </si>
+  <si>
+    <t>FrЧИН-7</t>
+  </si>
+  <si>
+    <t>998 95 613 96 02</t>
+  </si>
+  <si>
+    <t>@fruzumchin_7</t>
+  </si>
+  <si>
+    <t>40.934389, 68.730345</t>
+  </si>
+  <si>
+    <t>Ziyodin sh., Ipak yo‘li ko‘chasi, 144 uy: г. Зиадин, улица Ипак Йули, дом 144</t>
+  </si>
+  <si>
+    <t>FrЗИН-7</t>
+  </si>
+  <si>
+    <t>998 99 124 04 45</t>
+  </si>
+  <si>
+    <t>@fr_zin_7</t>
+  </si>
+  <si>
+    <t>40.046282, 65.667427</t>
+  </si>
+  <si>
+    <t>Sho'rchi sh., Jarqishloq MFY, Serg'ayrat ko'chasi, 65 a uy : г. Шурчи, Жаркишлок МФИ, улица Сергайрат, дом 65 а</t>
+  </si>
+  <si>
+    <t>FrШУР-4</t>
+  </si>
+  <si>
+    <t>998 91 230 05 45</t>
+  </si>
+  <si>
+    <t>@Frshur4</t>
+  </si>
+  <si>
+    <t>37.990627, 67.812359</t>
+  </si>
+  <si>
+    <t>Samarqand sh., Botir Zokirov MFY, Sattepo dahasi, 195 uy: г. Самарканд, Ботир Зокиров МФИ, район Саттепо, дом 195</t>
+  </si>
+  <si>
+    <t>FrСМК-79</t>
+  </si>
+  <si>
+    <t>998 91 525 15 09</t>
+  </si>
+  <si>
+    <t>@fr_smk_79</t>
+  </si>
+  <si>
+    <t>39.636612, 66.912972</t>
+  </si>
+  <si>
+    <t>Xo'jaabot sh., Beshkaram MFY, Mustaqillik ko‘chasi, 2 a uy: г. Ходжаабат, МФЙ Бешкарам, улица Мустакиллик, дом 2 а</t>
+  </si>
+  <si>
+    <t>FrХЖА-5</t>
+  </si>
+  <si>
+    <t>998 50 731 85 31</t>
+  </si>
+  <si>
+    <t>@FrXJA5</t>
+  </si>
+  <si>
+    <t>40.661766, 72.574516</t>
+  </si>
+  <si>
+    <t>Sho'r-Qal'a sh., Ulug' yo'l ko'chasi, 42a uy: г. Шуркала, улица Улуг Йул, дом 42а</t>
+  </si>
+  <si>
+    <t>FrШКЛ-1</t>
+  </si>
+  <si>
+    <t>998 91 919 19 45</t>
+  </si>
+  <si>
+    <t>@FrSHKL1</t>
+  </si>
+  <si>
+    <t>41.484575, 60.569200</t>
+  </si>
+  <si>
+    <t>Chandir sh., Mirishkor tumani, Chandir ko‘chasi, 106 uy: г. Чандыр, Миришкорский район, улица Чандыр, дом 106</t>
+  </si>
+  <si>
+    <t>FrЧНД-1</t>
+  </si>
+  <si>
+    <t>998 97 674 06 68</t>
+  </si>
+  <si>
+    <t>@frchND1</t>
+  </si>
+  <si>
+    <t>38.891973, 65.211631</t>
+  </si>
+  <si>
+    <t>Marg‘ilon sh., Tamara Xonim ko'chasi, 64А uy: г. Маргилан, улица Тамарахоним, дом 64А</t>
+  </si>
+  <si>
+    <t>FrМРГ-9</t>
+  </si>
+  <si>
+    <t>998 70 317 03 32</t>
+  </si>
+  <si>
+    <t>frmrg9</t>
+  </si>
+  <si>
+    <t>40.445478, 71.721186</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -19691,7 +20029,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -19704,8 +20042,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -19728,38 +20072,72 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-0.499984740745262"/>
+      </left>
+      <right style="thin">
+        <color theme="0" tint="-0.499984740745262"/>
+      </right>
+      <top style="thin">
+        <color theme="0" tint="-0.499984740745262"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -20065,7 +20443,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E1636"/>
+  <dimension ref="A1:E1658"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="58.28515625" style="1" customWidth="1"/>
@@ -47870,20 +48248,394 @@
       </c>
     </row>
     <row r="1636" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
-      <c r="A1636" s="5" t="s">
+      <c r="A1636" s="10" t="s">
         <v>6534</v>
       </c>
-      <c r="B1636" s="8" t="s">
+      <c r="B1636" s="11" t="s">
         <v>6535</v>
       </c>
-      <c r="C1636" s="7">
+      <c r="C1636" s="12">
         <v>705198868</v>
       </c>
-      <c r="D1636" s="8" t="s">
+      <c r="D1636" s="11" t="s">
         <v>6536</v>
       </c>
-      <c r="E1636" s="8" t="s">
+      <c r="E1636" s="11" t="s">
         <v>6537</v>
+      </c>
+    </row>
+    <row r="1637" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1637" s="5" t="s">
+        <v>6539</v>
+      </c>
+      <c r="B1637" s="13" t="s">
+        <v>6540</v>
+      </c>
+      <c r="C1637" s="14" t="s">
+        <v>6541</v>
+      </c>
+      <c r="D1637" s="8" t="s">
+        <v>6542</v>
+      </c>
+      <c r="E1637" s="8" t="s">
+        <v>6543</v>
+      </c>
+    </row>
+    <row r="1638" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1638" s="5" t="s">
+        <v>6544</v>
+      </c>
+      <c r="B1638" s="13" t="s">
+        <v>6545</v>
+      </c>
+      <c r="C1638" s="14" t="s">
+        <v>6546</v>
+      </c>
+      <c r="D1638" s="8" t="s">
+        <v>6547</v>
+      </c>
+      <c r="E1638" s="8" t="s">
+        <v>6548</v>
+      </c>
+    </row>
+    <row r="1639" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1639" s="5" t="s">
+        <v>6549</v>
+      </c>
+      <c r="B1639" s="13" t="s">
+        <v>6550</v>
+      </c>
+      <c r="C1639" s="14" t="s">
+        <v>6551</v>
+      </c>
+      <c r="D1639" s="8" t="s">
+        <v>6552</v>
+      </c>
+      <c r="E1639" s="8" t="s">
+        <v>6553</v>
+      </c>
+    </row>
+    <row r="1640" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1640" s="5" t="s">
+        <v>6554</v>
+      </c>
+      <c r="B1640" s="13" t="s">
+        <v>6555</v>
+      </c>
+      <c r="C1640" s="14" t="s">
+        <v>6556</v>
+      </c>
+      <c r="D1640" s="8" t="s">
+        <v>6557</v>
+      </c>
+      <c r="E1640" s="8" t="s">
+        <v>6558</v>
+      </c>
+    </row>
+    <row r="1641" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1641" s="5" t="s">
+        <v>6559</v>
+      </c>
+      <c r="B1641" s="13" t="s">
+        <v>6560</v>
+      </c>
+      <c r="C1641" s="14" t="s">
+        <v>6561</v>
+      </c>
+      <c r="D1641" s="8" t="s">
+        <v>6562</v>
+      </c>
+      <c r="E1641" s="8" t="s">
+        <v>6563</v>
+      </c>
+    </row>
+    <row r="1642" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1642" s="5" t="s">
+        <v>6564</v>
+      </c>
+      <c r="B1642" s="13" t="s">
+        <v>6565</v>
+      </c>
+      <c r="C1642" s="14" t="s">
+        <v>6566</v>
+      </c>
+      <c r="D1642" s="8" t="s">
+        <v>6567</v>
+      </c>
+      <c r="E1642" s="8" t="s">
+        <v>6568</v>
+      </c>
+    </row>
+    <row r="1643" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1643" s="5" t="s">
+        <v>6569</v>
+      </c>
+      <c r="B1643" s="13" t="s">
+        <v>6570</v>
+      </c>
+      <c r="C1643" s="14" t="s">
+        <v>6571</v>
+      </c>
+      <c r="D1643" s="8" t="s">
+        <v>6572</v>
+      </c>
+      <c r="E1643" s="8" t="s">
+        <v>6573</v>
+      </c>
+    </row>
+    <row r="1644" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1644" s="5" t="s">
+        <v>6574</v>
+      </c>
+      <c r="B1644" s="13" t="s">
+        <v>6575</v>
+      </c>
+      <c r="C1644" s="14" t="s">
+        <v>6576</v>
+      </c>
+      <c r="D1644" s="8" t="s">
+        <v>6577</v>
+      </c>
+      <c r="E1644" s="8" t="s">
+        <v>6578</v>
+      </c>
+    </row>
+    <row r="1645" spans="1:5" ht="39" x14ac:dyDescent="0.25">
+      <c r="A1645" s="5" t="s">
+        <v>6579</v>
+      </c>
+      <c r="B1645" s="13" t="s">
+        <v>6580</v>
+      </c>
+      <c r="C1645" s="14" t="s">
+        <v>6581</v>
+      </c>
+      <c r="D1645" s="8" t="s">
+        <v>6582</v>
+      </c>
+      <c r="E1645" s="8" t="s">
+        <v>6583</v>
+      </c>
+    </row>
+    <row r="1646" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1646" s="5" t="s">
+        <v>6584</v>
+      </c>
+      <c r="B1646" s="13" t="s">
+        <v>6585</v>
+      </c>
+      <c r="C1646" s="14" t="s">
+        <v>6586</v>
+      </c>
+      <c r="D1646" s="8" t="s">
+        <v>6587</v>
+      </c>
+      <c r="E1646" s="8" t="s">
+        <v>6588</v>
+      </c>
+    </row>
+    <row r="1647" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1647" s="5" t="s">
+        <v>6589</v>
+      </c>
+      <c r="B1647" s="13" t="s">
+        <v>6590</v>
+      </c>
+      <c r="C1647" s="14" t="s">
+        <v>6591</v>
+      </c>
+      <c r="D1647" s="8" t="s">
+        <v>6592</v>
+      </c>
+      <c r="E1647" s="8" t="s">
+        <v>6593</v>
+      </c>
+    </row>
+    <row r="1648" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1648" s="5" t="s">
+        <v>6594</v>
+      </c>
+      <c r="B1648" s="13" t="s">
+        <v>6595</v>
+      </c>
+      <c r="C1648" s="14" t="s">
+        <v>6596</v>
+      </c>
+      <c r="D1648" s="8" t="s">
+        <v>6597</v>
+      </c>
+      <c r="E1648" s="8" t="s">
+        <v>6598</v>
+      </c>
+    </row>
+    <row r="1649" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1649" s="5" t="s">
+        <v>6599</v>
+      </c>
+      <c r="B1649" s="13" t="s">
+        <v>6600</v>
+      </c>
+      <c r="C1649" s="14" t="s">
+        <v>6601</v>
+      </c>
+      <c r="D1649" s="8" t="s">
+        <v>6602</v>
+      </c>
+      <c r="E1649" s="8" t="s">
+        <v>6603</v>
+      </c>
+    </row>
+    <row r="1650" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1650" s="5" t="s">
+        <v>6604</v>
+      </c>
+      <c r="B1650" s="13" t="s">
+        <v>6605</v>
+      </c>
+      <c r="C1650" s="14" t="s">
+        <v>6606</v>
+      </c>
+      <c r="D1650" s="8" t="s">
+        <v>6607</v>
+      </c>
+      <c r="E1650" s="8" t="s">
+        <v>6608</v>
+      </c>
+    </row>
+    <row r="1651" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1651" s="15" t="s">
+        <v>6609</v>
+      </c>
+      <c r="B1651" s="13" t="s">
+        <v>6610</v>
+      </c>
+      <c r="C1651" s="16" t="s">
+        <v>6611</v>
+      </c>
+      <c r="D1651" s="13" t="s">
+        <v>6612</v>
+      </c>
+      <c r="E1651" s="13" t="s">
+        <v>6613</v>
+      </c>
+    </row>
+    <row r="1652" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1652" s="5" t="s">
+        <v>6614</v>
+      </c>
+      <c r="B1652" s="13" t="s">
+        <v>6615</v>
+      </c>
+      <c r="C1652" s="14" t="s">
+        <v>6616</v>
+      </c>
+      <c r="D1652" s="8" t="s">
+        <v>6617</v>
+      </c>
+      <c r="E1652" s="8" t="s">
+        <v>6618</v>
+      </c>
+    </row>
+    <row r="1653" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1653" s="15" t="s">
+        <v>6619</v>
+      </c>
+      <c r="B1653" s="13" t="s">
+        <v>6620</v>
+      </c>
+      <c r="C1653" s="16" t="s">
+        <v>6621</v>
+      </c>
+      <c r="D1653" s="13" t="s">
+        <v>6622</v>
+      </c>
+      <c r="E1653" s="13" t="s">
+        <v>6623</v>
+      </c>
+    </row>
+    <row r="1654" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1654" s="5" t="s">
+        <v>6624</v>
+      </c>
+      <c r="B1654" s="13" t="s">
+        <v>6625</v>
+      </c>
+      <c r="C1654" s="14" t="s">
+        <v>6626</v>
+      </c>
+      <c r="D1654" s="8" t="s">
+        <v>6627</v>
+      </c>
+      <c r="E1654" s="8" t="s">
+        <v>6628</v>
+      </c>
+    </row>
+    <row r="1655" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1655" s="5" t="s">
+        <v>6629</v>
+      </c>
+      <c r="B1655" s="13" t="s">
+        <v>6630</v>
+      </c>
+      <c r="C1655" s="14" t="s">
+        <v>6631</v>
+      </c>
+      <c r="D1655" s="8" t="s">
+        <v>6632</v>
+      </c>
+      <c r="E1655" s="8" t="s">
+        <v>6633</v>
+      </c>
+    </row>
+    <row r="1656" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1656" s="5" t="s">
+        <v>6634</v>
+      </c>
+      <c r="B1656" s="13" t="s">
+        <v>6635</v>
+      </c>
+      <c r="C1656" s="14" t="s">
+        <v>6636</v>
+      </c>
+      <c r="D1656" s="8" t="s">
+        <v>6637</v>
+      </c>
+      <c r="E1656" s="8" t="s">
+        <v>6638</v>
+      </c>
+    </row>
+    <row r="1657" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1657" s="5" t="s">
+        <v>6639</v>
+      </c>
+      <c r="B1657" s="13" t="s">
+        <v>6640</v>
+      </c>
+      <c r="C1657" s="14" t="s">
+        <v>6641</v>
+      </c>
+      <c r="D1657" s="8" t="s">
+        <v>6642</v>
+      </c>
+      <c r="E1657" s="8" t="s">
+        <v>6643</v>
+      </c>
+    </row>
+    <row r="1658" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1658" s="5" t="s">
+        <v>6644</v>
+      </c>
+      <c r="B1658" s="13" t="s">
+        <v>6645</v>
+      </c>
+      <c r="C1658" s="14" t="s">
+        <v>6646</v>
+      </c>
+      <c r="D1658" s="8" t="s">
+        <v>6647</v>
+      </c>
+      <c r="E1658" s="8" t="s">
+        <v>6648</v>
       </c>
     </row>
   </sheetData>
